--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>85013.49000000001</v>
+        <v>82092.52</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>42973.85</v>
+        <v>42018.78</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>27275.13</v>
+        <v>26668.95</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9213.620000000001</v>
+        <v>9008.85</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7447.02</v>
+        <v>7281.52</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43698.98</v>
+        <v>42439.6</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11520.54</v>
+        <v>11282.73</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>766143.0699999999</v>
+        <v>750328.3100000001</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>47232</v>
+        <v>46257.04</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>41132.12</v>
+        <v>40283.06</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>417442.81</v>
+        <v>405227.73</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10747.29</v>
+        <v>10432.81</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>21835.91</v>
+        <v>21843.55</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>56447.59</v>
+        <v>56556.21</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>20768.36</v>
+        <v>20918.87</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>18875.61</v>
+        <v>19012.41</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>16342.08</v>
+        <v>16460.51</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>39349.31</v>
+        <v>39248.25</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>246401.07</v>
+        <v>245768.22</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>71127.05</v>
+        <v>71961.64</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13584.72</v>
+        <v>13762.33</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>48135.83</v>
+        <v>48768.71</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>69500.2</v>
+        <v>70413.96000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>64701.81</v>
+        <v>65552.49000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10503.61</v>
+        <v>10773.86</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>60879.62</v>
+        <v>61680.12</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>28960.64</v>
+        <v>29282.56</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>72797.08</v>
+        <v>73440.07000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>386079.54</v>
+        <v>388618.51</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>33506.77</v>
+        <v>33771.89</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>676558.0699999999</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>203660.91</v>
+        <v>205272.38</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>69732.42</v>
+        <v>70162.33</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>84032.19</v>
+        <v>84040.89</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>68820.44</v>
+        <v>68827.57000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>46501.24</v>
+        <v>46506.05</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>19618.5</v>
+        <v>19620.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Instituto Nacional de Neurocirugía</t>
+          <t>Instituto de Neurocirugía</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>Fernando Marcelo</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ADOLFO IGNACIO</t>
+          <t>Adolfo Ignacio</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENVISION INVERSIONES LIMITADA </t>
+          <t>ENVISION INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ARCHIVO NACIONAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>VICTORIA SPA</t>
+          <t>VICTORIA SpA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SolNet SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Superintendencia de Electricidad y Combustibles</t>
+          <t>SUPERINTENDENCIA DE ELECTRICIDAD Y COMBUSTIBLES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Pragma Informatica S.A.</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Esta</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DISEÑO Y DESARROLLO VISUALMENTE SPA</t>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -623,7 +623,11 @@
           <t>76.811.563-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +997,11 @@
           <t>77.063.770-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>76.967.524-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1314,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1379,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1505,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1631,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1696,11 @@
           <t>77.681.168-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1761,11 @@
           <t>76.188.587-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1887,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2074,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2161,7 +2213,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1725-267-CM26</t>
+          <t>1057547-5944-SE26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,43 +2238,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.714.387-5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>73440.07000000001</v>
+        <v>49532.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057539-2804-CM26</t>
+          <t>1725-267-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,53 +2293,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+          <t>SOCIEDAD PROFESIONAL  VALIO LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.132.093-9</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>77.714.387-5</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>388618.51</v>
+        <v>73440.07000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2581-5-CM26</t>
+          <t>1057539-2804-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2358,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,27 +2368,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.070.200-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCHALI</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOSAFE</t>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.376.088-k</t>
+          <t>76.132.093-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2398,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>33771.89</v>
+        <v>388618.51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1186229-57-CM26</t>
+          <t>2581-5-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,12 +2429,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>69.070.200-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE CONCHALI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,28 +2444,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PRAGMA INFORMATICA S.A.</t>
+          <t>SOSAFE</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.063.770-8</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.376.088-k</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>681911.34</v>
+        <v>33771.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5403-17-CM26</t>
+          <t>1186229-57-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,12 +2494,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2509,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LIVISTER CHILE SPA</t>
+          <t>PRAGMA INFORMATICA S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.622.841-9</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>77.063.770-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>205272.38</v>
+        <v>681911.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1093219-9-CM26</t>
+          <t>5403-17-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,22 +2549,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,28 +2574,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>LIVISTER CHILE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>77.622.841-9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>70162.33</v>
+        <v>205272.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>770-51-CM26</t>
+          <t>1093219-9-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2614,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2624,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.604.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,28 +2639,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.083.021-6</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>96.986.170-4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>84040.89</v>
+        <v>70162.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>621923-19-SE26</t>
+          <t>770-51-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,12 +2689,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>53.314.945-6</t>
+          <t>60.604.000-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,32 +2704,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOFTGROUP SERVICIOS COMPUTACIONALES LIMITADA</t>
+          <t>SOCIEDAD DE SERVICIOS INFORMATICOS EN RED, LAZOS, S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.388.870-1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.083.021-6</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>68827.57000000001</v>
+        <v>84040.89</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2109-868-CM26</t>
+          <t>621923-19-SE26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2678,12 +2750,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>53.314.945-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,28 +2765,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>SOFTGROUP SERVICIOS COMPUTACIONALES LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>77.388.870-1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>46506.05</v>
+        <v>68827.57000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1305504-68-CM26</t>
+          <t>2109-868-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2734,32 +2810,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.981.100-3</t>
+          <t>61.608.203-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Diseño y Desarrollo Visualmente SpA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.046.871-1</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,6 +2845,67 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
+        <v>46506.05</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1305504-68-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.981.100-3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Diseño y Desarrollo Visualmente SpA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.046.871-1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
         <v>19620.53</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/abr-2026.xlsx
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
